--- a/templates/forms/1-17/2026-10-17.zh-hans/original.xlsx
+++ b/templates/forms/1-17/2026-10-17.zh-hans/original.xlsx
@@ -221,8 +221,8 @@
     <t xml:space="preserve">实施计划</t>
   </si>
   <si>
-    <t xml:space="preserve">是否
-有　委托</t>
+    <t xml:space="preserve">委托
+有　无</t>
   </si>
   <si>
     <t xml:space="preserve">支援工作人员或受托的实施负责人</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">ｃ．协助办理电、水、燃气等生活基础设施相关的手续</t>
   </si>
   <si>
-    <t xml:space="preserve">４　实施生活基础教育</t>
+    <t xml:space="preserve">４　实施生活入职教育</t>
   </si>
   <si>
     <t xml:space="preserve">ａ．在日本生活的一般事项</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">ｃ．咨询及投诉的联系方式、应提出申请的国家或地方公共团体机构的联系方式</t>
   </si>
   <si>
-    <t xml:space="preserve">４　实施生活基础教育
+    <t xml:space="preserve">４　实施生活入职教育
 （续）</t>
   </si>
   <si>
@@ -669,7 +669,7 @@
  ・ 面谈对象希望当面面谈</t>
   </si>
   <si>
-    <t xml:space="preserve">ｂ．为了再次确认，再次提供在生活基础教育中提供过的信息</t>
+    <t xml:space="preserve">ｂ．为了再次确认，再次提供在生活入职教育中提供过的信息</t>
   </si>
   <si>
     <t xml:space="preserve">□ 无线电或船舶电话（仅限渔船渔业）</t>
@@ -754,118 +754,114 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Noto Sans CJK SC"/>
       <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="13"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="Noto Serif CJK SC"/>
       <family val="1"/>
-      <charset val="128"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="13"/>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="Noto Serif CJK SC"/>
       <family val="1"/>
-      <charset val="128"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="Noto Serif CJK SC"/>
       <family val="1"/>
-      <charset val="128"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="Noto Serif CJK SC"/>
       <family val="1"/>
-      <charset val="128"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="13"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Noto Sans CJK SC"/>
       <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="20"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="Noto Sans CJK SC"/>
       <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="Noto Serif CJK SC"/>
       <family val="1"/>
-      <charset val="128"/>
+      <charset val="134"/>
     </font>
     <font>
       <strike/>
       <sz val="13"/>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="Noto Serif CJK SC"/>
       <family val="1"/>
-      <charset val="128"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="Noto Serif CJK SC"/>
       <family val="1"/>
-      <charset val="128"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="13"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="Noto Serif CJK SC"/>
       <family val="1"/>
-      <charset val="128"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="Noto Serif CJK SC"/>
       <family val="1"/>
-      <charset val="128"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="Noto Serif CJK SC"/>
       <family val="1"/>
-      <charset val="128"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="Noto Serif CJK SC"/>
       <family val="1"/>
-      <charset val="128"/>
+      <charset val="134"/>
     </font>
     <font>
       <strike/>
       <sz val="13"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="Noto Serif CJK SC"/>
       <family val="1"/>
-      <charset val="128"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="Noto Serif CJK SC"/>
       <family val="1"/>
-      <charset val="128"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
